--- a/семинар_пакет/04_приложения_и_реестры/INTERNATIONAL_PRACTICES.xlsx
+++ b/семинар_пакет/04_приложения_и_реестры/INTERNATIONAL_PRACTICES.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2088,117 +2088,6 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>I-sci_life</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Hori S. et al. Штатные диетологи по нацбазе LIFE (medRxiv, 2025)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Япония / medRxiv</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://www.medrxiv.org/content/10.1101/2025.11.01.25339287.abstract</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Научная публикация (препринт)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Проверено 02.08.2026</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Гл.9; раздел о японском опыте</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>I-sci_iddsi24</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Griffin H. et al. Применение IDDSI персоналом домов ухода (IJLCD, 2024)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Великобритания / Wiley</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://onlinelibrary.wiley.com/doi/abs/10.1111/1460-6984.13015</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Научная публикация</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Проверено 02.08.2026</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Гл.9–10; внедрение IDDSI через обучение</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>I-sci_mbm</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Cartwright J. et al. Maggie Beer's Big Mission — модель трапезы (BMC Geriatrics, 2026)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Австралия / Springer</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/article/10.1186/s12877-026-07690-6</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Научная публикация</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Проверено 02.08.2026</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Гл.4, 11; выбор блюд и достоинство жителей</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/семинар_пакет/04_приложения_и_реестры/INTERNATIONAL_PRACTICES.xlsx
+++ b/семинар_пакет/04_приложения_и_реестры/INTERNATIONAL_PRACTICES.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2088,6 +2088,43 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>I-easyread</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Великобритания: Accessible Information Standard — информация для пациентов с нарушениями предоставляется в доступных форматах (включая easy read: короткие фразы + изображения); Mencap — методические материалы</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NHS England / Mencap, Великобритания</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.mencap.org.uk/help-and-advice/health/accessible-information-standard</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>проверено 17.08.2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>глава 15, приложение 38 (памятка easy read)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
